--- a/data/trans_dic/P17G_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,74; 97,81</t>
+          <t>93,29; 97,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94,15; 98,16</t>
+          <t>93,9; 98,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,6; 99,21</t>
+          <t>95,48; 99,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96,27; 99,69</t>
+          <t>96,22; 99,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,32; 98,93</t>
+          <t>96,38; 99,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,43; 99,02</t>
+          <t>96,39; 98,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,37; 98,23</t>
+          <t>94,31; 98,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,81; 98,87</t>
+          <t>95,85; 98,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95,96; 98,2</t>
+          <t>95,89; 98,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96,14; 98,27</t>
+          <t>96,14; 98,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95,47; 98,29</t>
+          <t>95,59; 98,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,59; 98,96</t>
+          <t>96,56; 98,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,53; 92,43</t>
+          <t>84,26; 92,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,23; 94,83</t>
+          <t>88,92; 95,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,9; 93,23</t>
+          <t>87,43; 93,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,22; 93,33</t>
+          <t>86,31; 93,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,81; 94,35</t>
+          <t>88,77; 94,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,08; 98,39</t>
+          <t>95,21; 98,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,13; 96,25</t>
+          <t>92,22; 96,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,09; 95,01</t>
+          <t>89,4; 95,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,24; 92,77</t>
+          <t>88,05; 92,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,36; 96,58</t>
+          <t>93,34; 96,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,17; 94,46</t>
+          <t>91,1; 94,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,23; 93,56</t>
+          <t>89,13; 93,71</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,52; 80,49</t>
+          <t>56,93; 80,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,85; 90,17</t>
+          <t>70,59; 90,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,61; 86,45</t>
+          <t>70,65; 86,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70,64; 85,42</t>
+          <t>70,28; 84,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,45; 87,68</t>
+          <t>72,37; 88,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,15; 88,55</t>
+          <t>70,87; 87,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,4; 88,33</t>
+          <t>74,77; 88,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,38; 78,82</t>
+          <t>66,39; 78,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,6; 83,75</t>
+          <t>70,6; 83,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74,44; 87,06</t>
+          <t>73,49; 86,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75,35; 85,54</t>
+          <t>74,83; 85,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,39; 80,04</t>
+          <t>70,06; 80,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,23; 92,74</t>
+          <t>87,9; 92,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,24; 95,15</t>
+          <t>91,07; 95,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,1; 93,25</t>
+          <t>89,14; 93,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,84; 92,03</t>
+          <t>86,91; 92,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,25; 95,2</t>
+          <t>91,97; 95,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,54; 97,04</t>
+          <t>94,5; 97,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,34; 95,29</t>
+          <t>92,15; 95,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,19; 92,53</t>
+          <t>88,42; 92,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,25; 93,91</t>
+          <t>91,11; 93,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,67; 95,91</t>
+          <t>93,64; 95,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91,46; 93,82</t>
+          <t>91,3; 93,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,4; 91,87</t>
+          <t>88,42; 91,85</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135583</t>
+          <t>135582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>313253; 326866</t>
+          <t>311754; 326238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>317726; 331266</t>
+          <t>316881; 330932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>246902; 256227</t>
+          <t>246586; 256213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132384; 137082</t>
+          <t>132311; 137057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>508638; 522395</t>
+          <t>508932; 523059</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>521865; 535898</t>
+          <t>521620; 535222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>388122; 403989</t>
+          <t>387863; 404269</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>227642; 234908</t>
+          <t>227733; 234790</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>827414; 846741</t>
+          <t>826834; 846885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>844728; 863464</t>
+          <t>844723; 864161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>639179; 658072</t>
+          <t>640013; 657805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>362306; 371212</t>
+          <t>362201; 371072</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>211208; 230950</t>
+          <t>210516; 231164</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>313696; 337132</t>
+          <t>316121; 338139</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>404915; 429496</t>
+          <t>402754; 429659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>318703; 344994</t>
+          <t>319036; 345029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>358909; 381303</t>
+          <t>358781; 380752</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>462597; 478707</t>
+          <t>463256; 478594</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>538303; 562392</t>
+          <t>538828; 561594</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>447510; 477274</t>
+          <t>449076; 479076</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>577111; 606720</t>
+          <t>575832; 606466</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>786123; 813291</t>
+          <t>785971; 813242</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>952660; 987022</t>
+          <t>951969; 987510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>778094; 815873</t>
+          <t>777172; 817127</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42000; 57763</t>
+          <t>40861; 58100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53755; 67464</t>
+          <t>52814; 67515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84024; 104353</t>
+          <t>85274; 104665</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94288; 114019</t>
+          <t>93810; 113136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84144; 101841</t>
+          <t>84060; 102740</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76653; 95393</t>
+          <t>76347; 94203</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>103132; 122452</t>
+          <t>103646; 122820</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>101858; 120948</t>
+          <t>101887; 120775</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132674; 157382</t>
+          <t>132664; 156188</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135892; 158926</t>
+          <t>134153; 157551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>195394; 221820</t>
+          <t>194047; 221226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>201988; 229652</t>
+          <t>201040; 229556</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>578628; 608216</t>
+          <t>576484; 607664</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>700590; 730559</t>
+          <t>699275; 729420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>748135; 782950</t>
+          <t>748469; 782572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>556355; 589569</t>
+          <t>556762; 590180</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>967160; 998057</t>
+          <t>964140; 997163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1073478; 1101905</t>
+          <t>1073072; 1101984</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1047311; 1080758</t>
+          <t>1045157; 1078616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>787889; 826688</t>
+          <t>789926; 829885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1555133; 1600341</t>
+          <t>1552659; 1598206</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1782806; 1825525</t>
+          <t>1782153; 1825030</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1805211; 1851872</t>
+          <t>1802101; 1851859</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1356140; 1409275</t>
+          <t>1356380; 1408990</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,29; 97,62</t>
+          <t>93,62; 97,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,9; 98,06</t>
+          <t>94,07; 98,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,48; 99,21</t>
+          <t>95,17; 99,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96,22; 99,67</t>
+          <t>96,03; 99,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,38; 99,05</t>
+          <t>96,36; 98,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,39; 98,9</t>
+          <t>96,46; 98,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,31; 98,3</t>
+          <t>94,02; 98,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,85; 98,82</t>
+          <t>95,73; 98,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95,89; 98,22</t>
+          <t>96,02; 98,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96,14; 98,35</t>
+          <t>96,21; 98,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95,59; 98,25</t>
+          <t>95,55; 98,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,56; 98,92</t>
+          <t>96,62; 98,99</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,26; 92,52</t>
+          <t>84,48; 92,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,92; 95,11</t>
+          <t>88,86; 95,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,43; 93,27</t>
+          <t>87,45; 93,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,31; 93,34</t>
+          <t>86,3; 93,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,77; 94,21</t>
+          <t>88,99; 94,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,21; 98,36</t>
+          <t>95,53; 98,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,22; 96,12</t>
+          <t>92,32; 96,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,4; 95,37</t>
+          <t>88,51; 93,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,05; 92,73</t>
+          <t>88,44; 92,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,34; 96,58</t>
+          <t>93,37; 96,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,1; 94,5</t>
+          <t>91,03; 94,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,13; 93,71</t>
+          <t>88,4; 92,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,93; 80,95</t>
+          <t>57,46; 81,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,59; 90,24</t>
+          <t>72,27; 90,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,65; 86,71</t>
+          <t>69,82; 85,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70,28; 84,76</t>
+          <t>70,92; 84,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,37; 88,46</t>
+          <t>72,09; 87,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70,87; 87,44</t>
+          <t>70,65; 87,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,77; 88,6</t>
+          <t>74,36; 88,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,39; 78,7</t>
+          <t>69,24; 80,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,6; 83,12</t>
+          <t>70,63; 83,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,49; 86,31</t>
+          <t>74,05; 86,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74,83; 85,31</t>
+          <t>75,55; 86,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,06; 80,0</t>
+          <t>72,26; 80,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,9; 92,66</t>
+          <t>87,93; 92,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,07; 95,0</t>
+          <t>91,0; 95,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,14; 93,2</t>
+          <t>89,06; 93,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,91; 92,12</t>
+          <t>86,39; 91,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,97; 95,12</t>
+          <t>92,06; 95,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,5; 97,05</t>
+          <t>94,56; 97,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,15; 95,1</t>
+          <t>92,29; 95,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,42; 92,89</t>
+          <t>88,14; 91,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,11; 93,78</t>
+          <t>91,35; 93,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,89</t>
+          <t>93,6; 95,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91,3; 93,82</t>
+          <t>91,43; 93,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,42; 91,85</t>
+          <t>88,25; 91,1</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135582</t>
+          <t>145066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>232204</t>
+          <t>251517</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>367787</t>
+          <t>396583</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>311754; 326238</t>
+          <t>312883; 326125</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>316881; 330932</t>
+          <t>317466; 331380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>246586; 256213</t>
+          <t>245788; 256219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132311; 137057</t>
+          <t>141297; 146677</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>508932; 523059</t>
+          <t>508843; 522474</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>521620; 535222</t>
+          <t>522034; 535291</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>387863; 404269</t>
+          <t>386688; 403689</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>227733; 234790</t>
+          <t>246334; 254606</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>826834; 846885</t>
+          <t>827918; 846883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>844723; 864161</t>
+          <t>845368; 863940</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>640013; 657805</t>
+          <t>639759; 657811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>362201; 371072</t>
+          <t>390767; 400386</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>334069</t>
+          <t>357184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>462531</t>
+          <t>445659</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>796600</t>
+          <t>802843</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>210516; 231164</t>
+          <t>211077; 231372</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>316121; 338139</t>
+          <t>315927; 337960</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402754; 429659</t>
+          <t>402885; 429406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>319036; 345029</t>
+          <t>341940; 368676</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>358781; 380752</t>
+          <t>359638; 382463</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>463256; 478594</t>
+          <t>464785; 479492</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>538828; 561594</t>
+          <t>539381; 562302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>449076; 479076</t>
+          <t>433297; 455623</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>575832; 606466</t>
+          <t>578368; 608139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>785971; 813242</t>
+          <t>786209; 813220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>951969; 987510</t>
+          <t>951209; 986068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>777172; 817127</t>
+          <t>783009; 818086</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104833</t>
+          <t>114883</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>112014</t>
+          <t>132500</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>216846</t>
+          <t>247384</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40861; 58100</t>
+          <t>41242; 58205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52814; 67515</t>
+          <t>54076; 67665</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85274; 104665</t>
+          <t>84276; 103385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93810; 113136</t>
+          <t>103818; 124301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84060; 102740</t>
+          <t>83729; 101624</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76347; 94203</t>
+          <t>76112; 94719</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>103646; 122820</t>
+          <t>103077; 122815</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>101887; 120775</t>
+          <t>121837; 142362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132664; 156188</t>
+          <t>132723; 156840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134153; 157551</t>
+          <t>135180; 158077</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194047; 221226</t>
+          <t>195922; 223444</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>201040; 229556</t>
+          <t>232921; 260863</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574485</t>
+          <t>617134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>806750</t>
+          <t>829676</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1381234</t>
+          <t>1446810</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>576484; 607664</t>
+          <t>576662; 607753</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>699275; 729420</t>
+          <t>698715; 729753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>748469; 782572</t>
+          <t>747805; 781025</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>556762; 590180</t>
+          <t>595891; 633362</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>964140; 997163</t>
+          <t>965119; 997968</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1073072; 1101984</t>
+          <t>1073713; 1102090</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1045157; 1078616</t>
+          <t>1046724; 1080629</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>789926; 829885</t>
+          <t>813321; 843183</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1552659; 1598206</t>
+          <t>1556823; 1599828</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1782153; 1825030</t>
+          <t>1781570; 1823694</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1802101; 1851859</t>
+          <t>1804681; 1852713</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1356380; 1408990</t>
+          <t>1423090; 1468991</t>
         </is>
       </c>
     </row>
